--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 24,8</t>
+          <t>15,1; 24,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,33; 56,35</t>
+          <t>44,38; 56,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,59; 43,45</t>
+          <t>30,59; 42,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 24,18</t>
+          <t>7,58; 24,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 20,71</t>
+          <t>12,18; 20,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,46; 57,54</t>
+          <t>45,76; 57,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,42; 52,92</t>
+          <t>40,68; 52,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 33,05</t>
+          <t>15,07; 32,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,21</t>
+          <t>14,51; 20,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,24; 55,68</t>
+          <t>46,81; 55,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,52; 46,4</t>
+          <t>36,97; 46,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,12</t>
+          <t>13,21; 25,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,43; 34,04</t>
+          <t>24,91; 34,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,25; 60,02</t>
+          <t>50,1; 60,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,44; 61,21</t>
+          <t>50,57; 61,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,6; 36,58</t>
+          <t>20,08; 37,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,07; 38,83</t>
+          <t>29,87; 38,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,8</t>
+          <t>72,11; 79,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,9; 69,59</t>
+          <t>61,27; 69,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 35,36</t>
+          <t>13,31; 34,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,24; 35,28</t>
+          <t>29,13; 35,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,08; 69,23</t>
+          <t>63,2; 69,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57,7; 64,86</t>
+          <t>58,01; 64,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,73; 32,85</t>
+          <t>17,73; 33,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,53; 31,19</t>
+          <t>23,15; 31,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,83; 76,64</t>
+          <t>68,97; 76,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,68; 65,42</t>
+          <t>56,72; 65,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 36,81</t>
+          <t>27,03; 37,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 33,73</t>
+          <t>26,54; 33,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,34; 79,76</t>
+          <t>73,43; 79,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,02; 68,7</t>
+          <t>61,23; 68,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,47; 30,75</t>
+          <t>18,66; 30,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,21; 31,34</t>
+          <t>26,11; 31,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,23; 77,28</t>
+          <t>72,41; 77,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,37; 66,09</t>
+          <t>60,35; 66,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,74; 32,24</t>
+          <t>24,37; 32,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 19,87</t>
+          <t>12,66; 20,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,26; 59,54</t>
+          <t>50,56; 59,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,71; 45,89</t>
+          <t>36,11; 45,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 27,86</t>
+          <t>19,82; 27,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 23,52</t>
+          <t>15,7; 23,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,11; 49,1</t>
+          <t>40,43; 48,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,44; 45,3</t>
+          <t>36,37; 45,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 25,01</t>
+          <t>17,5; 25,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,61</t>
+          <t>15,25; 20,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,15; 53,1</t>
+          <t>46,08; 52,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,06; 43,62</t>
+          <t>37,22; 43,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,95; 25,38</t>
+          <t>19,66; 25,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,35; 19,13</t>
+          <t>11,36; 19,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,55; 35,47</t>
+          <t>25,22; 35,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,38; 28,51</t>
+          <t>19,03; 28,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,63</t>
+          <t>15,31; 23,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,37; 25,51</t>
+          <t>16,52; 25,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,42; 37,4</t>
+          <t>27,46; 37,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,07; 31,0</t>
+          <t>21,95; 31,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,88</t>
+          <t>16,65; 22,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,51</t>
+          <t>14,92; 20,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,95; 34,66</t>
+          <t>28,05; 34,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,29; 28,98</t>
+          <t>22,02; 28,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,95</t>
+          <t>16,91; 22,18</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,81</t>
+          <t>10,64; 18,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,09; 35,01</t>
+          <t>24,4; 35,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,84; 27,29</t>
+          <t>18,26; 27,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 14,46</t>
+          <t>9,4; 14,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,48; 28,13</t>
+          <t>19,82; 28,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,39; 31,3</t>
+          <t>21,51; 30,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,56; 32,0</t>
+          <t>22,53; 32,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 76,55</t>
+          <t>15,27; 78,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,3; 22,4</t>
+          <t>16,13; 22,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,42; 31,33</t>
+          <t>24,03; 31,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,61; 28,44</t>
+          <t>21,56; 28,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,56; 63,53</t>
+          <t>13,53; 64,84</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,37; 34,74</t>
+          <t>22,02; 34,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,78; 53,15</t>
+          <t>39,38; 52,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,44; 42,0</t>
+          <t>31,41; 41,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,59; 34,28</t>
+          <t>25,83; 34,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,23; 37,77</t>
+          <t>27,44; 37,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,05; 55,7</t>
+          <t>44,87; 55,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,43; 53,85</t>
+          <t>42,99; 54,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,35; 47,23</t>
+          <t>40,13; 47,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,95; 35,21</t>
+          <t>26,63; 35,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,49; 53,29</t>
+          <t>44,51; 53,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,79; 47,86</t>
+          <t>39,54; 47,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,6; 40,98</t>
+          <t>35,39; 40,53</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,24; 23,52</t>
+          <t>20,23; 23,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,81; 53,79</t>
+          <t>49,74; 53,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,52; 43,46</t>
+          <t>39,73; 43,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,95</t>
+          <t>21,06; 24,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,72; 27,85</t>
+          <t>24,54; 27,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,36; 55,89</t>
+          <t>52,24; 55,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,1; 48,91</t>
+          <t>45,12; 48,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,01; 46,79</t>
+          <t>25,08; 47,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,03; 25,45</t>
+          <t>23,06; 25,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,69; 54,52</t>
+          <t>51,7; 54,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43,1; 45,9</t>
+          <t>43,2; 45,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,28</t>
+          <t>23,9; 38,44</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37898; 62343</t>
+          <t>37950; 62368</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115759; 147133</t>
+          <t>115893; 148161</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68950; 97940</t>
+          <t>68945; 96845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13159; 43037</t>
+          <t>13486; 43727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36044; 61207</t>
+          <t>36009; 60058</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>140822; 174408</t>
+          <t>138697; 174063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98324; 128750</t>
+          <t>98971; 127355</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21866; 48225</t>
+          <t>21987; 47787</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80750; 116019</t>
+          <t>79365; 114761</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266563; 314170</t>
+          <t>264132; 311179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175852; 217450</t>
+          <t>173293; 216360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42697; 81357</t>
+          <t>42777; 82313</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>109211; 146187</t>
+          <t>106971; 147071</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>235872; 276230</t>
+          <t>230587; 276791</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170501; 206902</t>
+          <t>170935; 207778</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39838; 70748</t>
+          <t>38832; 71786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>148163; 191331</t>
+          <t>147215; 191877</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>361361; 399486</t>
+          <t>360964; 398722</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>266021; 303986</t>
+          <t>267656; 304681</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51912; 129454</t>
+          <t>48748; 127363</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>269680; 325349</t>
+          <t>268648; 325117</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>606135; 665202</t>
+          <t>607277; 666835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447043; 502535</t>
+          <t>449509; 502794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99212; 183837</t>
+          <t>99225; 185643</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>130111; 172454</t>
+          <t>127979; 171616</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>423857; 471919</t>
+          <t>424710; 470248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>297068; 342916</t>
+          <t>297289; 342056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103851; 140870</t>
+          <t>103459; 142773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>171493; 217718</t>
+          <t>171281; 218741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>487357; 530071</t>
+          <t>488013; 530310</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>358894; 404086</t>
+          <t>360159; 405517</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100854; 159278</t>
+          <t>96643; 159973</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314085; 375541</t>
+          <t>312870; 376005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>924846; 989452</t>
+          <t>927148; 989604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>671516; 735131</t>
+          <t>671276; 737205</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>213845; 290440</t>
+          <t>219555; 293203</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52528; 81370</t>
+          <t>51859; 82062</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>248602; 294504</t>
+          <t>250074; 296258</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178486; 223138</t>
+          <t>175592; 221438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88326; 122280</t>
+          <t>86977; 121814</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65655; 97893</t>
+          <t>65371; 96435</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>212685; 260371</t>
+          <t>214356; 259413</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>181330; 225381</t>
+          <t>180969; 225616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88292; 129000</t>
+          <t>90262; 128943</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>126269; 170145</t>
+          <t>125951; 171565</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473024; 544217</t>
+          <t>472295; 542690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>364639; 429162</t>
+          <t>366222; 429962</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>190462; 242278</t>
+          <t>187720; 240934</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36292; 61154</t>
+          <t>36314; 61528</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92101; 127865</t>
+          <t>90928; 127435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66262; 97456</t>
+          <t>65046; 98545</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51654; 78150</t>
+          <t>50637; 78819</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56734; 88397</t>
+          <t>57261; 87027</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>111974; 152714</t>
+          <t>112133; 151196</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93369; 131139</t>
+          <t>92856; 132520</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59223; 81427</t>
+          <t>59270; 80501</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>97956; 136638</t>
+          <t>99435; 138241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>214895; 266482</t>
+          <t>215680; 266149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170474; 221601</t>
+          <t>168433; 220016</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>114615; 150690</t>
+          <t>116106; 152275</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31455; 54871</t>
+          <t>31022; 54769</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73954; 107500</t>
+          <t>74916; 108761</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58529; 89515</t>
+          <t>59915; 90011</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33068; 52690</t>
+          <t>34236; 53610</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>66810; 96470</t>
+          <t>67982; 98681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75312; 110196</t>
+          <t>75729; 109010</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82957; 117663</t>
+          <t>82867; 119372</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>94606; 465093</t>
+          <t>92751; 476815</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>103447; 142152</t>
+          <t>102332; 141656</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>160964; 206490</t>
+          <t>158351; 208040</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150349; 197895</t>
+          <t>150021; 195608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131842; 617467</t>
+          <t>131489; 630253</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46944; 72909</t>
+          <t>46220; 71459</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>99015; 132272</t>
+          <t>98013; 131576</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80261; 107232</t>
+          <t>80193; 106771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71976; 96428</t>
+          <t>72658; 96028</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90933; 126125</t>
+          <t>91621; 125762</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>173282; 214271</t>
+          <t>172589; 213646</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>168256; 213540</t>
+          <t>170461; 215166</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>171268; 200458</t>
+          <t>170317; 200210</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>146543; 191477</t>
+          <t>144804; 190930</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281864; 337598</t>
+          <t>282001; 336678</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>259354; 311990</t>
+          <t>257716; 312145</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>251221; 289227</t>
+          <t>249723; 286048</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>498707; 579750</t>
+          <t>498664; 585848</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1368979; 1478154</t>
+          <t>1366860; 1474978</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>987571; 1086042</t>
+          <t>992738; 1089928</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>458338; 541364</t>
+          <t>456947; 536612</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>710346; 800129</t>
+          <t>705160; 801015</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1645976; 1756874</t>
+          <t>1642075; 1759869</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1331846; 1444516</t>
+          <t>1332406; 1446870</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>733652; 1372674</t>
+          <t>735655; 1404661</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1229084; 1358587</t>
+          <t>1231143; 1358193</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3045590; 3212455</t>
+          <t>3046118; 3207681</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2350037; 2502291</t>
+          <t>2355148; 2502314</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1224278; 1953711</t>
+          <t>1219515; 1961677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 24,81</t>
+          <t>14,94; 24,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,38; 56,74</t>
+          <t>43,73; 56,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,59; 42,97</t>
+          <t>30,43; 43,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 24,56</t>
+          <t>10,79; 30,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 20,32</t>
+          <t>12,09; 20,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,76; 57,43</t>
+          <t>46,13; 57,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,68; 52,35</t>
+          <t>40,66; 52,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 32,75</t>
+          <t>17,79; 35,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 20,98</t>
+          <t>14,1; 20,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,81; 55,15</t>
+          <t>47,02; 55,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,97; 46,16</t>
+          <t>37,61; 46,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 25,41</t>
+          <t>16,04; 28,92</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 34,25</t>
+          <t>25,09; 34,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,1; 60,14</t>
+          <t>51,13; 60,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,57; 61,47</t>
+          <t>50,58; 61,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,08; 37,11</t>
+          <t>23,77; 39,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,87; 38,94</t>
+          <t>30,12; 39,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,11; 79,65</t>
+          <t>72,14; 79,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,27; 69,75</t>
+          <t>60,51; 69,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 34,78</t>
+          <t>28,58; 39,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,13; 35,25</t>
+          <t>29,15; 35,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,2; 69,4</t>
+          <t>63,28; 69,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,01; 64,89</t>
+          <t>57,99; 64,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,73; 33,18</t>
+          <t>28,22; 37,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,15; 31,04</t>
+          <t>23,23; 31,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,97; 76,36</t>
+          <t>69,02; 76,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,72; 65,26</t>
+          <t>56,37; 65,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,03; 37,3</t>
+          <t>28,0; 37,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,89</t>
+          <t>26,46; 33,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,43; 79,8</t>
+          <t>73,37; 80,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,23; 68,94</t>
+          <t>61,21; 68,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 30,88</t>
+          <t>26,62; 33,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,11; 31,38</t>
+          <t>25,8; 31,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,41; 77,29</t>
+          <t>72,39; 77,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,35; 66,28</t>
+          <t>60,36; 65,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,37; 32,55</t>
+          <t>28,47; 34,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 20,04</t>
+          <t>12,61; 19,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,56; 59,9</t>
+          <t>50,14; 59,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,11; 45,54</t>
+          <t>36,56; 45,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 27,75</t>
+          <t>20,79; 29,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 23,17</t>
+          <t>15,4; 23,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,43; 48,92</t>
+          <t>39,97; 49,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,37; 45,34</t>
+          <t>35,86; 44,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 25,0</t>
+          <t>21,47; 27,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,78</t>
+          <t>15,3; 20,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,08; 52,95</t>
+          <t>46,16; 53,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,22; 43,7</t>
+          <t>37,5; 43,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 25,24</t>
+          <t>22,15; 27,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,24</t>
+          <t>10,97; 19,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,22; 35,35</t>
+          <t>24,77; 35,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 28,83</t>
+          <t>19,18; 28,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 23,84</t>
+          <t>15,84; 24,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,11</t>
+          <t>16,4; 25,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,46; 37,03</t>
+          <t>27,43; 37,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,95; 31,33</t>
+          <t>21,95; 31,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 22,62</t>
+          <t>16,35; 22,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,92; 20,75</t>
+          <t>15,03; 20,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 34,62</t>
+          <t>27,7; 34,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,02; 28,77</t>
+          <t>22,31; 28,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,18</t>
+          <t>17,39; 22,29</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,64; 18,78</t>
+          <t>10,68; 18,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,4; 35,42</t>
+          <t>24,04; 35,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 27,44</t>
+          <t>17,72; 27,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,71</t>
+          <t>9,03; 14,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,82; 28,78</t>
+          <t>19,52; 28,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,51; 30,96</t>
+          <t>21,69; 31,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,53; 32,46</t>
+          <t>22,97; 32,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 78,47</t>
+          <t>14,23; 19,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,32</t>
+          <t>16,58; 22,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,03; 31,56</t>
+          <t>24,39; 31,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,56; 28,11</t>
+          <t>21,91; 28,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,53; 64,84</t>
+          <t>12,46; 16,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,02; 34,05</t>
+          <t>22,69; 34,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,38; 52,87</t>
+          <t>39,57; 53,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,41; 41,82</t>
+          <t>31,14; 41,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 34,14</t>
+          <t>24,97; 34,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,44; 37,66</t>
+          <t>27,45; 37,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,87; 55,54</t>
+          <t>44,95; 55,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,99; 54,26</t>
+          <t>42,53; 53,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,13; 47,17</t>
+          <t>40,0; 46,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,63; 35,11</t>
+          <t>26,51; 34,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,51; 53,14</t>
+          <t>44,25; 52,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,54; 47,89</t>
+          <t>39,52; 47,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,39; 40,53</t>
+          <t>34,97; 40,56</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,77</t>
+          <t>20,06; 23,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,74; 53,67</t>
+          <t>49,73; 53,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,73; 43,61</t>
+          <t>39,59; 43,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,74</t>
+          <t>22,17; 25,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,88</t>
+          <t>24,55; 27,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,24; 55,98</t>
+          <t>52,37; 55,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,12; 48,99</t>
+          <t>45,03; 48,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,08; 47,88</t>
+          <t>26,41; 29,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,06; 25,44</t>
+          <t>23,05; 25,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,7; 54,44</t>
+          <t>51,58; 54,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43,2; 45,9</t>
+          <t>43,03; 45,77</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,9; 38,44</t>
+          <t>24,95; 27,22</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>45374</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>77177</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37950; 62368</t>
+          <t>37559; 61763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115893; 148161</t>
+          <t>114173; 147388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68945; 96845</t>
+          <t>68597; 98978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13486; 43727</t>
+          <t>18490; 51389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36009; 60058</t>
+          <t>35742; 60145</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>138697; 174063</t>
+          <t>139814; 173478</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98971; 127355</t>
+          <t>98925; 128713</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21987; 47787</t>
+          <t>31429; 63017</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79365; 114761</t>
+          <t>77092; 113834</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>264132; 311179</t>
+          <t>265267; 311327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173293; 216360</t>
+          <t>176256; 218094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>42777; 82313</t>
+          <t>55819; 100615</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97734</t>
+          <t>113896</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>151388</t>
+          <t>183400</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106971; 147071</t>
+          <t>107764; 146940</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>230587; 276791</t>
+          <t>235351; 276636</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170935; 207778</t>
+          <t>170954; 207964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38832; 71786</t>
+          <t>52542; 87848</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>147215; 191877</t>
+          <t>148441; 192555</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>360964; 398722</t>
+          <t>361102; 399165</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>267656; 304681</t>
+          <t>264301; 304290</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48748; 127363</t>
+          <t>96587; 133617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>268648; 325117</t>
+          <t>268834; 326611</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>607277; 666835</t>
+          <t>608027; 667230</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>449509; 502794</t>
+          <t>449294; 500713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99225; 185643</t>
+          <t>157755; 211196</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121202</t>
+          <t>143860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>259308</t>
+          <t>303732</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127979; 171616</t>
+          <t>128437; 171821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>424710; 470248</t>
+          <t>425038; 469966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>297289; 342056</t>
+          <t>295476; 341229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103459; 142773</t>
+          <t>122350; 164514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>171281; 218741</t>
+          <t>170795; 216373</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>488013; 530310</t>
+          <t>487554; 532138</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>360159; 405517</t>
+          <t>360038; 404626</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96643; 159973</t>
+          <t>143448; 180463</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>312870; 376005</t>
+          <t>309184; 374361</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>927148; 989604</t>
+          <t>926894; 991390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>671276; 737205</t>
+          <t>671428; 733110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>219555; 293203</t>
+          <t>277843; 333826</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105524</t>
+          <t>120486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>216797</t>
+          <t>247920</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51859; 82062</t>
+          <t>51626; 81480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>250074; 296258</t>
+          <t>248023; 293643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175592; 221438</t>
+          <t>177784; 221495</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86977; 121814</t>
+          <t>100096; 141552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65371; 96435</t>
+          <t>64113; 97389</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>214356; 259413</t>
+          <t>211943; 264038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>180969; 225616</t>
+          <t>178418; 223794</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90262; 128943</t>
+          <t>113216; 144205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125951; 171565</t>
+          <t>126339; 171995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>472295; 542690</t>
+          <t>473119; 543572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>366222; 429962</t>
+          <t>368946; 431058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>187720; 240934</t>
+          <t>223413; 273953</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63815</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>146930</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36314; 61528</t>
+          <t>35084; 61555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90928; 127435</t>
+          <t>89290; 126499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65046; 98545</t>
+          <t>65568; 96904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50637; 78819</t>
+          <t>55989; 85612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57261; 87027</t>
+          <t>56821; 87742</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112133; 151196</t>
+          <t>112019; 151603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92856; 132520</t>
+          <t>92822; 131914</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59270; 80501</t>
+          <t>65216; 91344</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99435; 138241</t>
+          <t>100128; 138286</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>215680; 266149</t>
+          <t>212959; 265409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168433; 220016</t>
+          <t>170631; 219534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>116106; 152275</t>
+          <t>130800; 167703</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42396</t>
+          <t>46262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>269918</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>312314</t>
+          <t>119436</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31022; 54769</t>
+          <t>31151; 54396</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>74916; 108761</t>
+          <t>73817; 108474</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59915; 90011</t>
+          <t>58134; 88730</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34236; 53610</t>
+          <t>36354; 57537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67982; 98681</t>
+          <t>66935; 97019</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75729; 109010</t>
+          <t>76367; 109334</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82867; 119372</t>
+          <t>84456; 118111</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92751; 476815</t>
+          <t>62390; 85879</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102332; 141656</t>
+          <t>105206; 143328</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>158351; 208040</t>
+          <t>160775; 208976</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150021; 195608</t>
+          <t>152427; 199307</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>131489; 630253</t>
+          <t>104770; 135186</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>185009</t>
+          <t>200750</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>268964</t>
+          <t>291186</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>46220; 71459</t>
+          <t>47631; 73124</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>98013; 131576</t>
+          <t>98474; 133800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80193; 106771</t>
+          <t>79515; 107194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72658; 96028</t>
+          <t>77045; 105181</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91621; 125762</t>
+          <t>91665; 126014</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>172589; 213646</t>
+          <t>172904; 212964</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>170461; 215166</t>
+          <t>168644; 213854</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>170317; 200210</t>
+          <t>185235; 215679</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>144804; 190930</t>
+          <t>144159; 190293</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282001; 336678</t>
+          <t>280349; 334104</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257716; 312145</t>
+          <t>257633; 311832</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>249723; 286048</t>
+          <t>269789; 312929</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>498664; 585848</t>
+          <t>494437; 581117</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1366860; 1474978</t>
+          <t>1366682; 1477050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>992738; 1089928</t>
+          <t>989298; 1093685</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>456947; 536612</t>
+          <t>526661; 616392</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>705160; 801015</t>
+          <t>705373; 797847</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1642075; 1759869</t>
+          <t>1646138; 1755358</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1332406; 1446870</t>
+          <t>1329864; 1438320</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>735655; 1404661</t>
+          <t>761055; 840593</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1231143; 1358193</t>
+          <t>1230628; 1358434</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3046118; 3207681</t>
+          <t>3038954; 3202251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2355148; 2502314</t>
+          <t>2346271; 2495542</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1219515; 1961677</t>
+          <t>1311410; 1430828</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
